--- a/fund-fix-or-stop/Fund_Fix_or_Stop_Templates.xlsx
+++ b/fund-fix-or-stop/Fund_Fix_or_Stop_Templates.xlsx
@@ -22,9 +22,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General tool value plan" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor checklist" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90-day tracker" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example threshold sheet" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Red memo" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example value confirmation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charter" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery checklist" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gateway controls" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent approval" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality plan" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value plan" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recovery and incident" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example threshold sheet" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Red memo" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example value confirmation" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +45,7 @@
     <numFmt numFmtId="165" formatCode="$0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +74,12 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -118,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +163,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -538,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -610,178 +626,286 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Self-assessment</t>
+          <t>What to customize</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chapter 1. Ten questions and a score.</t>
+          <t>Every yellow cell, plus the limits, sample sizes, deadlines and the delegated funding limit, which the book gives only as defaults.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Blank or example</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chapter 3. One row per use case: the twelve fields, the contract renewal date, and whether the investment is mandatory.</t>
+          <t>Sheets named Example hold completed records for the fictional bank. Every other sheet is a blank template.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Explore entry</t>
+          <t>Self-assessment</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chapter 13. One-page scoring of new ideas; eligibility and ranking are calculated.</t>
+          <t>Chapter 1. Ten questions and a score.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Intake and tiering</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chapter 4. Six answers; the highest sets the tier.</t>
+          <t>Chapter 3. One row per use case: the twelve fields, the contract renewal date, and whether the investment is mandatory.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Threshold sheet</t>
+          <t>Explore entry</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chapter 11. Limits, readings, and status by rule, including the trend rule with a minimum decline.</t>
+          <t>Chapter 13. One-page scoring of new ideas; eligibility and ranking are calculated.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Five-test scorecard</t>
+          <t>Intake and tiering</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chapter 7. Overall status is the weakest test.</t>
+          <t>Chapter 4. Six answers; the highest sets the tier.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Value leakage</t>
+          <t>Threshold sheet</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chapter 9. Business case, four leaks, measured and realized value.</t>
+          <t>Chapter 11. Limits, readings, and status by rule, including the trend rule with a minimum decline.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Monthly cost report</t>
+          <t>Five-test scorecard</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chapter 10. Unit cost against plan with default Economics status.</t>
+          <t>Chapter 7. Overall status is the weakest test.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Leadership page</t>
+          <t>Value leakage</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chapter 14. Spend by status from a list of investments.</t>
+          <t>Chapter 9. Business case, four leaks, measured and realized value.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Gate decision</t>
+          <t>Monthly cost report</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chapter 13. Record of a fund, fix once, or stop decision.</t>
+          <t>Chapter 10. Unit cost against plan with default Economics status.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Red decision memo</t>
+          <t>Leadership page</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chapter 14. The five sections of the memo.</t>
+          <t>Chapter 14. Spend by status from a list of investments.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>General tool value plan</t>
+          <t>Gate decision</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chapter 17. Role-based hypotheses and task-sampling results.</t>
+          <t>Chapter 13. Record of a fund, fix once, or stop decision.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Vendor checklist</t>
+          <t>Red decision memo</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Appendix D. Due-diligence questions, what each answer decides, and the vendor's answers.</t>
+          <t>Chapter 14. The five sections of the memo.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>90-day tracker</t>
+          <t>General tool value plan</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chapter 15. Activities, owners, and dates.</t>
+          <t>Chapter 17. Role-based hypotheses and task-sampling results.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Vendor checklist</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Appendix D. Due-diligence questions, what each answer decides, and the vendor's answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>90-day tracker</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 15. Activities, owners, and dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Charter</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 2. Review board charter, with the book's example beside each section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Discovery checklist</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 3. Quarterly sweep for AI that registration missed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Gateway controls</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 5. Control checklist per use case, and the model selection record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Agent approval</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 6. Agent approval record and promotion checklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Quality plan</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 8. Test set, live sample, reviewers and grader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Value plan</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 9. Baseline, comparison, calculation, payback and Finance confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Recovery and incident</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 12. Recovery plan and incident record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Example sheets</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Three completed records from Appendix A, filled in for Fytvio: a threshold sheet, a Red decision memo, and a value confirmation with live formulas. They show the level of detail that lets a record stand as evidence.</t>
         </is>
@@ -2340,180 +2464,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Completed threshold sheet: customer service assistant (Chapter 11)</t>
+          <t>AI review board charter (Chapter 2)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Completed example from Appendix A, for the fictional bank Fytvio. Use it as a guide to the level of detail; record your own in the blank template.</t>
+          <t>The charter should fit on one page. Write your entry in the yellow column; the right-hand column shows the book's fictional example.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Entry</t>
+          <t>What to write</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Your entry</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Example (Fytvio)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Use case</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Customer service assistant. High tier. Run stage.</t>
+          <t>Why the review board exists, in one or two sentences</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Approve, oversee, and make funding recommendations on all AI used at Fytvio</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Signatures</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Business owner (head of customer services) and AI governance lead, signed and dated. Review board approval recorded in its minutes.</t>
+          <t>Which AI is covered</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Platforms and the uses on them; built, bought, embedded SaaS features, agents, existing ML models</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Version</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Version 2. Re-approved after the test set was rebuilt (Chapter 8). Version 1 kept on file.</t>
+          <t>What stays with existing reviews</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Business case, architecture fit, contracts, data rights</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Exceptions in force</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Chair and members</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Named roles, not people</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Chief data and AI officer (chair); chief risk officer (co-chair, veto on risk); CISO; CPO; Compliance; Finance; Enterprise Architecture; business-unit AI leads attend for their items</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Critical errors reaching customers</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Secretary</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Hard constraint. Any one is Red, with no Amber band. Reason: the assistant is customer-facing and High tier. Source: live sample, complaints and grader flags, checked daily.</t>
+          <t>Who runs the review board</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AI governance lead</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Live accuracy</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Independence</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Performance limit. Green 90% or higher, Red below 86%. Reason: Green allows about two points of sampling variation below the 92% baseline; Red sits at the bottom of the sampling range for 150 samples. Minimum sample 150 a month; minimum decline 2.5 points. Source: reviewer-scored live sample, monthly.</t>
+          <t>Reporting line of the governance lead; role of internal audit</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Governance lead reports to the chief risk officer; internal audit observes and reviews annually</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Test-set accuracy</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>AI policy and exceptions</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Performance limit. Green 92% or higher, Red below 89%. Reason: set from the 94% baseline on 400 cases. Source: evaluation service, on every change and monthly.</t>
+          <t>Policy owner; how exceptions are approved and tracked</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AI policy approved by the executive committee; exceptions with expiry dates, reported quarterly</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Share of eligible questions handled</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Quorum</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Performance limit. Green 70% or higher, Red below 52.5%. Reason: default limits, 75% of the 70% target for Red, not rounded. Source: contact center system, monthly.</t>
+          <t>Minimum attendance to decide</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Chair or delegate, co-chair or delegate, plus security and privacy, plus a majority of members</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Unit cost per conversation</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Decision rights</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Performance limit. Green $0.198 or lower, Red above $0.225. Reason: default limits, 10% and 25% above the $0.18 plan. Source: cost metering, reconciled with the ledger monthly.</t>
+          <t>What the review board decides; what is delegated</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Board: platforms, High-tier investments, Red decisions, pause or retire; funds up to $500,000 per stage and recommends above it to the investment committee. Business-unit AI leads: Low and Medium tier in their units. Governance lead: standards, profiles, status</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Response time</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Escalation</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Performance limit. 95% of answers within 4 seconds is Green; above 6 seconds is Red. Reason: set from the 3.1-second baseline. Source: gateway, daily.</t>
+          <t>Where unresolved issues go</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Executive committee; funding through its investment committee</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Handle-time reduction</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Performance limit. Green 54 seconds or more, Red below 42 seconds. Reason: set from the 60-second target. Source: contact center system against the baseline; turned into realized value by Finance each quarter.</t>
+          <t>Meeting schedule</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Review board every 2 weeks; health review monthly; portfolio review quarterly</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Override rate and retrieval miss rate</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Records</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Leading signals. Above 15% and above 6% set Amber at most. Reason: they move before accuracy does. Source: gateway, weekly owner check.</t>
+          <t>Decision record format and storage</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Decision, conditions, reasons, dissent, evidence, next review date</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Performance targets</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>How the review board is measured</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>The six board measures in Chapter 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Charter review</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>When the charter is reviewed</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Annually, or after any Sev 1 incident</t>
         </is>
       </c>
     </row>
@@ -2528,148 +2772,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Completed Red decision memo: small-business lending agent (Chapter 14)</t>
+          <t>Discovery checklist (Chapter 3)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Completed example from Appendix A, for the fictional bank Fytvio. Use it as a guide to the level of detail; record your own in the blank template.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Investment</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Small-business lending agent (FYT-052). Pilot stage, month 2. Level 2: a relationship manager approves each email.</t>
+          <t>Run quarterly. Coverage = registered AI systems divided by discovered AI systems; the target is 95 percent or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Discovery sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Done?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Cause and evidence</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>The agent took rates from a document library that still held last quarter's rate sheet. The monthly live sample found one wrong quote; gateway logs found all 23 within two hours. Quotes were 0.25 to 0.5 percentage points too low. Approvals missed them because emails were approved in batches, some 30 or more in a few minutes.</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Invoices and accounts payable searched for AI vendors.</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Red the same day under the critical event rule. Agent paused. Other tests Green: value 92% of target, adoption 88%, cost below plan.</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Corporate card and expense records searched.</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Option 1: fix once</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Take rates from the pricing system, add 40 test cases, limit batch approval to ten emails and open every email with a price. Cost: team time and two more months of pilot running cost. Timing: two months to show the fix holds.</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>New and renewed contracts checked for AI features.</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Option 2: stop</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Write off pilot spend to date and return the remaining pilot budget to the portfolio pool. The time saving of about 5.5 hours a week per manager is lost.</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Single sign-on application authorizations reviewed.</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Customer and risk impact</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>23 businesses received wrong quotes; each was called with a corrected quote. Handled as a Sev 1 incident. Compliance is reviewing fair lending and state-law exposure.</t>
-        </is>
-      </c>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Network and proxy logs checked for traffic to AI services.</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Fix once. The cause is specific and testable, and the fix removes the model from writing rates.</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Cloud accounts scanned for AI services.</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Decision needed by</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Ten business days from the Red status.</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Release notes of major software platforms reviewed for new AI features.</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Decision and dissent</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Fix once, as recommended, with two months to show it holds. Dissent recorded: one member asked for a stop, on the grounds that Level 2 approval had failed and might fail again.</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Gateway access keys matched to inventory entries.</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Coverage calculated and reported; gaps assigned to an owner with a date.</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B6:B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2680,460 +2930,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Completed value confirmation: document intake (Chapter 9)</t>
+          <t>Gateway controls and model selection (Chapter 5)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Completed example from Appendix A, for the fictional bank Fytvio. Yellow cells are inputs; the rest calculate, so the example can be reused with your own figures.</t>
+          <t>One checklist per use case. Where a control lives outside the gateway, record where in the notes: vendor settings, identity, data-loss prevention, contract or platform logs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Gateway control checklist (per use case)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>In place?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Inventory number tagged on every call</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Personal and financial identifier patterns: redact or block</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Prompt injection screening on inputs and retrieved content</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Exact cases handled by rules before any model</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Approved model class; backup model pinned and passed the test set</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Prompt templates versioned; fixed portion cached</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Retrieval limited to user entitlements</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Tools from approved catalog only; inputs validated; read-only by default</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Output format validated</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Grounding check for document-based answers</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Output checks: hold or stream decision recorded</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Document sources: owner, effective and expiry dates, versions, freshness check</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Personal-data scan before display</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Full trace, tokens, cost, response time, and errors logged</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Model version pinned; test set run on every change</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Model selection record</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Use case and inventory number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Task type (classify, extract, summarize, answer, plan)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Test set and approved threshold</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Model classes tested, with accuracy for each</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Cost per task and response time for each model class tested</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Selected class, model, and pinned version</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Reason a lower class was not chosen</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Data terms confirmed (agreement, training, retention)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Hosting location and residency</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Cost techniques applied</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Approved by and date</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B6:B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Enforced,Verified,Contract only,Gap"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Agent approval record (Chapter 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Levels 1 and 2 can be approved at intake; Level 3 is earned after two clean periods at Level 2. Recommend-only is fixed at approval for irreversible actions on people or money.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Evidence or note</t>
+          <t>Entry</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Baseline minutes per document</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Measured for six weeks before launch</t>
-        </is>
-      </c>
+          <t>Agent name and inventory number</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Planned minutes per document</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Business case</t>
-        </is>
-      </c>
+          <t>Business owner and technical owner</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Documents per year</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Baseline period, annualized</t>
-        </is>
-      </c>
+          <t>Agent identity and systems it can access</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Loaded cost per hour ($)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Agreed with Finance in advance</t>
-        </is>
-      </c>
+          <t>Acts for users? Whose rights apply; actions needing more than the user’s rights</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Planned running cost per year ($)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Business case</t>
-        </is>
-      </c>
+          <t>Tool servers used, and tools allowed from each</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Business case gross benefit ($)</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>(B5-B6)/60*B7*B8</f>
-        <v/>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Minutes saved, in hours, times the loaded cost</t>
-        </is>
-      </c>
+          <t>Action types, with autonomy level for each</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Business case net benefit ($)</t>
-        </is>
-      </c>
-      <c r="B11" s="8">
-        <f>B10-B9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Leak (annual, entered as positive)</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Cause</t>
-        </is>
-      </c>
+          <t>Tools allowed for each action type</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Limits: steps per task, actions per day, spend per day</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Reads external content, such as email, customer uploads or web pages? (If yes, no write access)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Adoption gap</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>78% of eligible documents went through the system</t>
-        </is>
-      </c>
+          <t>Memory: what is stored, and for how long</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Process not redesigned</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Full field check kept</t>
-        </is>
-      </c>
+          <t>Checkpoints required before which actions</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Quality rework</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Handwritten form extraction errors</t>
-        </is>
-      </c>
+          <t>Handoff triggers and handoff summary format</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Cost overrun</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Largest model used for every document</t>
-        </is>
-      </c>
+          <t>Reversal procedure tested (date)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Measured net benefit ($)</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>B11-SUM(B14:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>First Finance review, two quarters into Scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
+          <t>Critical errors defined</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Measures: steps per task; actions reversed or blocked; plus five tests</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Promotion criteria and step-down rule</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Harvested</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>20 vacant intake positions not refilled, visible in the budget</t>
-        </is>
-      </c>
+          <t>Kill switch tested (date)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Redeployed</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Clerks moved to the loan-processing backlog, which fell by a measured amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Unharvested</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Capacity created, not yet used for named work; reported as capacity, not money</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Realized gross ($)</t>
-        </is>
-      </c>
-      <c r="B24" s="8">
-        <f>B21+B22</f>
-        <v/>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Harvested plus redeployed, confirmed by Finance at quarter-end</t>
-        </is>
-      </c>
+          <t>Approved by, date, and next review</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Full running cost ($)</t>
-        </is>
-      </c>
-      <c r="B25" s="8">
-        <f>B9+B17</f>
-        <v/>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Planned cost plus the overrun</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Realized net benefit ($)</t>
-        </is>
-      </c>
-      <c r="B26" s="8">
-        <f>B24-B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Compared with the net business case</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Promotion checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Met?</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Gross measured benefit ($)</t>
-        </is>
-      </c>
-      <c r="B27" s="8">
-        <f>B18+B25</f>
-        <v/>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Net benefit plus full running cost</t>
-        </is>
-      </c>
+          <t>Two consecutive review periods within all limits at the current level.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Check: classes add up to gross benefit</t>
-        </is>
-      </c>
-      <c r="B28" s="4">
-        <f>IF(ABS(SUM(B21:B23)-B27)&lt;1,"OK","Does not add up")</f>
-        <v/>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>The classes split gross benefit, before running cost</t>
-        </is>
-      </c>
+          <t>No critical errors in either period.</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Value-to-cost ratio</t>
-        </is>
-      </c>
-      <c r="B29" s="14">
-        <f>IF(B25=0,"",B27/B25)</f>
-        <v/>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Floor 1.5 at Scale and Run; Red below 1.0</t>
-        </is>
-      </c>
+          <t>Steps per task and actions reversed or blocked stable or improving.</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Measured net as share of business case</t>
-        </is>
-      </c>
-      <c r="B30" s="9">
-        <f>IF(B11=0,"",B18/B11)</f>
-        <v/>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Sets status at the Scale stage</t>
-        </is>
-      </c>
+          <t>Reversal procedure tested for the new level (if moving to Level 3). Recommend-only is fixed at approval and is not a promotion.</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Realized net as share of business case</t>
-        </is>
-      </c>
-      <c r="B31" s="9">
-        <f>IF(B11=0,"",B26/B11)</f>
-        <v/>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Sets status from the Run stage</t>
-        </is>
-      </c>
+          <t>Threshold sheet updated with limits for the new level.</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Value test (default limits)</t>
-        </is>
-      </c>
-      <c r="B32" s="4">
-        <f>IF(B30="","",IF(B30&gt;=0.9,"Green",IF(B30&gt;=0.7,"Amber","Red")))</f>
-        <v/>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>On measured value at Scale. Green at 90% or more of the business case; Amber 70 to 89%; Red below 70%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Next confirmation</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Next quarter-end, after the four fixes in Chapter 9</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
+          <t>Review board decision recorded, with the scope of the promotion stated by action type.</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B27:B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3361,6 +3778,1448 @@
       <formula1>"Yes,Partly,No"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quality measurement plan (Chapter 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sampling ranges use the 95 percent Wilson score interval by default. Grader calibration is a minimum condition, not proof of reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Use case and inventory number</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Test set: size, composition, and who approved the answers</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Test set: run triggers (every change; monthly) and refresh date</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Live sample: size and frequency for the tier, and stratification by topic</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Minimum samples for high-risk topics</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Reviewers (names or team) and confirmation they are independent</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Scoring guide version; definition of acceptable</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Passes correct, complete, grounded, safe</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Double-scoring: at least 50 items, pooled if needed; agreement target</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Kappa 0.6 or more, with percentage</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Automated grader: scope, calibration date, agreement with humans</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Decides status only at kappa 0.6 or more</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Critical, major, and minor errors defined for this use case</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Segment limits (if any)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Safety signals monitored (identifier blocks, injection attempts, output scan)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bias testing scope and schedule (High tier)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Where results are recorded and who confirms them</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Value measurement plan (Chapter 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Value counts as realized only when Finance confirms it, net of full running cost. Mandatory investments are scored on meeting the obligation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Use case and inventory number</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Benefit types (time, errors, revenue, recoveries, risk)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Baseline period (4–8 weeks) and dates</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Baseline: time per task, error rate, volume by type</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Comparison method (control group or adjusted before-and-after)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Control group description and matching</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Calculation formula and adoption adjustment</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Loaded cost per hour (agreed with Finance)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>One-time cost (Explore, Pilot, build, integration) and expected payback</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Process changes required, owner, and date</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Expected classification: harvested, redeployed, unharvested</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Named work for redeployed capacity and how its output is measured</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Finance contact and quarterly confirmation dates</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Current confidence level (modeled, measured, realized)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recovery plan and incident record (Chapter 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A recovery plan is due within 5 business days of Amber. A third consecutive decline is Red, whether or not a recovery plan exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Recovery plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Use case and inventory number</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Status and rule triggered (date)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Cause (or work to find it)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Actions, each with owner and date</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Measures that will show the fix worked</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Target date to meet limits</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Five conditions: root cause; fix tested; live results hold (2 periods); signals stable; governance lead confirms</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Date each met</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Escalation date if target is missed</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Incident record</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Incident number, use case, and severity</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Time detected, and how</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Containment action and time</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Users notified (time)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Affected interactions and people identified</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Corrections made and people contacted</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Compliance decision on reporting</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Test cases added; test set result before re-enabling</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Why detection took as long as it did</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Monitoring and limit changes</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Re-tiering or re-approval needed?</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Closed by (governance lead) and date</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Completed threshold sheet: customer service assistant (Chapter 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Completed example from Appendix A, for the fictional bank Fytvio. Use it as a guide to the level of detail; record your own in the blank template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Use case</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Customer service assistant. High tier. Run stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Business owner (head of customer services) and AI governance lead, signed and dated. Review board approval recorded in its minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Version 2. Re-approved after the test set was rebuilt (Chapter 8). Version 1 kept on file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Exceptions in force</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Critical errors reaching customers</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Hard constraint. Any one is Red, with no Amber band. Reason: the assistant is customer-facing and High tier. Source: live sample, complaints and grader flags, checked daily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Live accuracy</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Performance limit. Green 90% or higher, Red below 86%. Reason: Green allows about two points of sampling variation below the 92% baseline; Red sits just below the bottom of the sampling range for 150 samples. Minimum sample 150 a month; minimum decline 2.5 points. Source: reviewer-scored live sample, monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Test-set accuracy</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Performance limit. Green 92% or higher, Red below 89%. Reason: set from the 94% baseline on 400 cases. Source: evaluation service, on every change and monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Share of eligible questions handled</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Performance limit. Green 70% or higher, Red below 52.5%. Reason: default limits, 75% of the 70% target for Red, not rounded. Source: contact center system, monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Unit cost per conversation</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Performance limit. Green $0.198 or lower, Red above $0.225. Reason: default limits, 10% and 25% above the $0.18 plan. Source: cost metering, reconciled with the ledger monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Response time</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Performance limit. 95% of answers within 4 seconds is Green; above 6 seconds is Red. Reason: set from the 3.1-second baseline. Source: gateway, daily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Handle-time reduction</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Performance limit. Green 54 seconds or more, Red below 42 seconds. Reason: set from the 60-second target. Source: contact center system against the baseline; turned into realized value by Finance each quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Override rate and retrieval miss rate</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Leading signals. Above 15% and above 6% set Amber at most. Reason: they move before accuracy does. Source: gateway, weekly owner check.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Completed Red decision memo: small-business lending agent (Chapter 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Completed example from Appendix A, for the fictional bank Fytvio. Use it as a guide to the level of detail; record your own in the blank template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Small-business lending agent (FYT-052). Pilot stage, month 2. Level 2: a relationship manager approves each email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Cause and evidence</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>The agent took rates from a document library that still held last quarter's rate sheet. The monthly live sample found one wrong quote; gateway logs found all 23 within two hours. Quotes were 0.25 to 0.5 percentage points too low. Approvals missed them because emails were approved in batches, some 30 or more in a few minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Red the same day under the critical event rule. Agent paused. Other tests Green: value 92% of target, adoption 88%, cost below plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Option 1: fix once</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Take rates from the pricing system, add 40 test cases, limit batch approval to ten emails and open every email with a price. Cost: team time and two more months of pilot running cost. Timing: two months to show the fix holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Option 2: stop</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Write off pilot spend to date and return the remaining pilot budget to the portfolio pool. The time saving of about 5.5 hours a week per manager is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Customer and risk impact</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>23 businesses received wrong quotes; each was called with a corrected quote. Handled as a Sev 1 incident. Compliance is reviewing fair lending and state-law exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Fix once. The cause is specific and testable, and the fix removes the model from writing rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Decision needed by</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ten business days from the Red status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Decision and dissent</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Fix once, as recommended, with two months to show it holds. Dissent recorded: one member asked for a stop, on the grounds that Level 2 approval had failed and might fail again.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Completed value confirmation: document intake (Chapter 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Completed example from Appendix A, for the fictional bank Fytvio. Yellow cells are inputs; the rest calculate, so the example can be reused with your own figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Evidence or note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Baseline minutes per document</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Measured for six weeks before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Planned minutes per document</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Business case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Documents per year</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Baseline period, annualized</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Loaded cost per hour ($)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Agreed with Finance in advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Planned running cost per year ($)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Business case</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Business case gross benefit ($)</t>
+        </is>
+      </c>
+      <c r="B10" s="8">
+        <f>(B5-B6)/60*B7*B8</f>
+        <v/>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Minutes saved, in hours, times the loaded cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Business case net benefit ($)</t>
+        </is>
+      </c>
+      <c r="B11" s="8">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Leak (annual, entered as positive)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Adoption gap</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>78% of eligible documents went through the system</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Process not redesigned</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Full field check kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Quality rework</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>900000</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Handwritten form extraction errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Cost overrun</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Largest model used for every document</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Measured net benefit ($)</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>B11-SUM(B14:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>First Finance review, two quarters into Scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Harvested</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>20 vacant intake positions not refilled, visible in the budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Redeployed</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Clerks moved to the loan-processing backlog, which fell by a measured amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Unharvested</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Capacity created, not yet used for named work; reported as capacity, not money</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Realized gross ($)</t>
+        </is>
+      </c>
+      <c r="B24" s="8">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Harvested plus redeployed, confirmed by Finance at quarter-end</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Full running cost ($)</t>
+        </is>
+      </c>
+      <c r="B25" s="8">
+        <f>B9+B17</f>
+        <v/>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Planned cost plus the overrun</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Realized net benefit ($)</t>
+        </is>
+      </c>
+      <c r="B26" s="8">
+        <f>B24-B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Compared with the net business case</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Gross measured benefit ($)</t>
+        </is>
+      </c>
+      <c r="B27" s="8">
+        <f>B18+B25</f>
+        <v/>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Net benefit plus full running cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Check: classes add up to gross benefit</t>
+        </is>
+      </c>
+      <c r="B28" s="4">
+        <f>IF(ABS(SUM(B21:B23)-B27)&lt;1,"OK","Does not add up")</f>
+        <v/>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>The classes split gross benefit, before running cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Value-to-cost ratio</t>
+        </is>
+      </c>
+      <c r="B29" s="15">
+        <f>IF(B25=0,"",B27/B25)</f>
+        <v/>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Floor 1.5 at Scale and Run; Red below 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Measured net as share of business case</t>
+        </is>
+      </c>
+      <c r="B30" s="9">
+        <f>IF(B11=0,"",B18/B11)</f>
+        <v/>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Sets status at the Scale stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Realized net as share of business case</t>
+        </is>
+      </c>
+      <c r="B31" s="9">
+        <f>IF(B11=0,"",B26/B11)</f>
+        <v/>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Sets status from the Run stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Value test (default limits)</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>IF(B30="","",IF(B30&gt;=0.9,"Green",IF(B30&gt;=0.7,"Amber","Red")))</f>
+        <v/>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>On measured value at Scale. Green at 90% or more of the business case; Amber 70 to 89%; Red below 70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Next confirmation</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Next quarter-end, after the four fixes in Chapter 9</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5055,7 +6914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5225,7 +7084,7 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>Green allows about two points of sampling variation below the 92% baseline; Red at the bottom of the sampling range for 150 samples</t>
+          <t>Green allows about two points of sampling variation below the 92% baseline; Red just below the bottom of the sampling range for 150 samples</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
@@ -5681,9 +7540,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Sampled measures: a single reading below Green sets a watch and the next sample is doubled; a second low reading confirms Amber. A reading whose whole range sits below the Red limit is Red at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Trend: a third consecutive decline is Red, whether or not a recovery plan exists. Add earlier periods to the sheet to track it.</t>
         </is>
       </c>
     </row>
